--- a/docentes/Morales Vallejo Jorge Luis - Estadisticos 20211.xlsx
+++ b/docentes/Morales Vallejo Jorge Luis - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="28">
   <si>
     <t>Mat</t>
   </si>
@@ -76,73 +76,31 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>CLEMENTE</t>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
   </si>
   <si>
     <t>DOLORES</t>
   </si>
   <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
-    <t>CHULIN</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
+    <t>PEREZ</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>MONTERO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>LIZBETH</t>
-  </si>
-  <si>
-    <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>PERLA</t>
+    <t>ANDRES</t>
+  </si>
+  <si>
+    <t>CARLOS EMILIO</t>
   </si>
   <si>
     <t>ZURISADAI</t>
-  </si>
-  <si>
-    <t>DARLA MARLENE</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>CESAR SAID</t>
-  </si>
-  <si>
-    <t>IVANNA DANIELA</t>
   </si>
 </sst>
 </file>
@@ -543,19 +501,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>70.97</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -569,19 +527,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>80.56</v>
+        <v>88.89</v>
       </c>
       <c r="H3">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -595,19 +553,19 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G4">
-        <v>83.72</v>
+        <v>88.37</v>
       </c>
       <c r="H4">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -621,19 +579,19 @@
         <v>43</v>
       </c>
       <c r="D5">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G5">
-        <v>74.42</v>
+        <v>88.37</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>
@@ -686,16 +644,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="E2">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>80.65000000000001</v>
+      </c>
+      <c r="H2">
+        <v>7.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -709,16 +670,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="E3">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>77.78</v>
+      </c>
+      <c r="H3">
+        <v>8.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -732,16 +696,19 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="E4">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>81.40000000000001</v>
+      </c>
+      <c r="H4">
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -755,16 +722,19 @@
         <v>43</v>
       </c>
       <c r="D5">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="E5">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>79.06999999999999</v>
+      </c>
+      <c r="H5">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -817,19 +787,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>70.97</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -843,19 +813,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>80.56</v>
+        <v>88.89</v>
       </c>
       <c r="H3">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -869,19 +839,19 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G4">
-        <v>83.72</v>
+        <v>88.37</v>
       </c>
       <c r="H4">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -895,19 +865,19 @@
         <v>43</v>
       </c>
       <c r="D5">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G5">
-        <v>74.42</v>
+        <v>88.37</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -917,7 +887,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -949,62 +919,62 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920233</v>
+        <v>21330051920289</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920358</v>
+        <v>21330051920294</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920295</v>
+        <v>21330051920299</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1013,122 +983,7 @@
         <v>12</v>
       </c>
       <c r="G4">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920299</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920304</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920327</v>
-      </c>
-      <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920192</v>
-      </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920326</v>
-      </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" t="s">
-        <v>41</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Morales Vallejo Jorge Luis - Estadisticos 20211.xlsx
+++ b/docentes/Morales Vallejo Jorge Luis - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -79,28 +79,10 @@
     <t>APALE</t>
   </si>
   <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>DOLORES</t>
-  </si>
-  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>ANDRES</t>
-  </si>
-  <si>
-    <t>CARLOS EMILIO</t>
-  </si>
-  <si>
-    <t>ZURISADAI</t>
   </si>
 </sst>
 </file>
@@ -887,7 +869,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -925,10 +907,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -938,52 +920,6 @@
       </c>
       <c r="G2">
         <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920294</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920299</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Morales Vallejo Jorge Luis - Estadisticos 20211.xlsx
+++ b/docentes/Morales Vallejo Jorge Luis - Estadisticos 20211.xlsx
@@ -704,7 +704,7 @@
         <v>43</v>
       </c>
       <c r="D5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E5">
         <v>6</v>
@@ -716,7 +716,7 @@
         <v>79.06999999999999</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Morales Vallejo Jorge Luis - Estadisticos 20211.xlsx
+++ b/docentes/Morales Vallejo Jorge Luis - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="25">
   <si>
     <t>Mat</t>
   </si>
@@ -79,10 +79,19 @@
     <t>APALE</t>
   </si>
   <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>ANDRES</t>
+  </si>
+  <si>
+    <t>CARLOS EMILIO</t>
   </si>
 </sst>
 </file>
@@ -480,22 +489,22 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>87.09999999999999</v>
+        <v>90.63</v>
       </c>
       <c r="H2">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -509,10 +518,10 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F3">
         <v>32</v>
@@ -521,7 +530,7 @@
         <v>88.89</v>
       </c>
       <c r="H3">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -535,10 +544,10 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F4">
         <v>38</v>
@@ -547,7 +556,7 @@
         <v>88.37</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -561,10 +570,10 @@
         <v>43</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F5">
         <v>38</v>
@@ -573,7 +582,7 @@
         <v>88.37</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -623,22 +632,22 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>80.65000000000001</v>
+        <v>90.63</v>
       </c>
       <c r="H2">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -652,19 +661,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>77.78</v>
+        <v>83.33</v>
       </c>
       <c r="H3">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -678,19 +687,19 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G4">
-        <v>81.40000000000001</v>
+        <v>86.05</v>
       </c>
       <c r="H4">
-        <v>8.300000000000001</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -704,19 +713,19 @@
         <v>43</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G5">
-        <v>79.06999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -766,22 +775,22 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
         <v>4</v>
       </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
       <c r="F2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>87.09999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="H2">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -795,19 +804,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>88.89</v>
+        <v>86.11</v>
       </c>
       <c r="H3">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -821,19 +830,19 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G4">
-        <v>88.37</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -847,19 +856,19 @@
         <v>43</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F5">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G5">
-        <v>88.37</v>
+        <v>83.72</v>
       </c>
       <c r="H5">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -869,7 +878,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -907,10 +916,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -919,7 +928,30 @@
         <v>12</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>21330051920294</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
